--- a/data/trans_orig/IP07KS_C02_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C02_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse lleno/a de energía en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de sentirse lleno/a de energía, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29343</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22659</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38742</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16460</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11834</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20518</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>52,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22728</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>23164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46866</t>
+          <t>47557</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37209</t>
+          <t>38649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59273</t>
+          <t>58250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13353</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6645</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19439</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12314</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8526</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17065</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>39,5%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>17841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>26714</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33826</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,83%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8035</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1719</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5482</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5514</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2978</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8028</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4260</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4512</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3882</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>952</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>750</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53837</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42607</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>63826</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32761</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26411</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38041</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>61,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>35059</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41113</t>
+          <t>28659</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63695</t>
+          <t>41063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>86694</t>
+          <t>88895</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>76723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98662</t>
+          <t>101339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25265</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43933</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>24,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16775</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11785</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22795</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>31,28%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33832</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24734</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43177</t>
+          <t>23945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>50606</t>
+          <t>51577</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39593</t>
+          <t>40964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62167</t>
+          <t>63411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9984</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4157</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>22,15%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3345</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2156</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8167</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2538</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>8645</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2248</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7608</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2411</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7795</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6431</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2946</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,22 +1939,22 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47537</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36599</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>54428</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>83,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>59293</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>48220</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68598</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>66,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>95,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48598</t>
+          <t>36431</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39374</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56002</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>107892</t>
+          <t>83967</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94215</t>
+          <t>71442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123019</t>
+          <t>92982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16994</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9871</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27855</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>11668</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3075</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21765</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>27651</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41070</t>
+          <t>41250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -2310,107 +2310,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1222</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4948</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>4666</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1222</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>5412</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -2536,107 +2536,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2663</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1573</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2314</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>32995</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>25593</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>39028</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>60,18%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>46,68%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>71,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>28060</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>21672</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>33856</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>52,47%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>40,52%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>63,3%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33434</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>23594</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39503</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>61494</t>
+          <t>62671</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>53923</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>72666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,06%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20215</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14278</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>27867</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>36,87%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>50,83%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>21325</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>15539</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>27403</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>29,05%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>51,24%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>22439</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>41342</t>
+          <t>42655</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32605</t>
+          <t>32845</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50245</t>
+          <t>51476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>5224</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,53%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>4098</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>7991</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>54829</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>54829</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>54829</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>108618</t>
+          <t>111695</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>108618</t>
+          <t>111695</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>108618</t>
+          <t>111695</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>163711</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>146448</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>181516</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>54,42%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>67,45%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>136574</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>119750</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>165248</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>56,9%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>78,51%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>166372</t>
+          <t>119379</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>148053</t>
+          <t>106870</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>185299</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>302946</t>
+          <t>283091</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>281090</t>
+          <t>261038</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>336945</t>
+          <t>302017</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>84654</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>68859</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>101604</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>31,46%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>25,59%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>37,76%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>62081</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>37962</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>76506</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>36,35%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>82684</t>
+          <t>64968</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>53831</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>99353</t>
+          <t>77034</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>149622</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>130502</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>14606</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>28714</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>10384</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>5591</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>17239</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37399</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>42332</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>3031</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>8450</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>7775</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>4759</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>8008</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>10053</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>1736</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
